--- a/event_evaluation_forms/014_event_logistics_assessment_questionnaire--event_evaluation_forms.xlsx
+++ b/event_evaluation_forms/014_event_logistics_assessment_questionnaire--event_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -531,14 +531,14 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,20 +548,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Planning</t>
+          <t>Event Start Date</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Event End Date</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +594,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Venue</t>
+          <t>Event Location</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,13 +617,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Food and Beverage</t>
+          <t>Number of Attendees</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,13 +640,13 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Event Budget</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -663,20 +663,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Evaluation</t>
+          <t>Event Type</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,20 +686,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Review and Recommendations</t>
+          <t>Event Status</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,20 +709,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Review and Recommendations</t>
+          <t>Venue Description</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,20 +732,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Review and Recommendations</t>
+          <t>Communication Plan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,20 +755,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Review and Recommendations</t>
+          <t>Evaluation Criteria</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -783,75 +783,6 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>event_logistics_assessment_questionnaire_page_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Review and Recommendations</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>event_logistics_assessment_questionnaire_page_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Review and Recommendations</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>event_logistics_assessment_questionnaire_page_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Review and Recommendations</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -868,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -896,102 +827,119 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>event_logistics_assessment_questionnaire_page_2_choices</t>
+          <t>event_logistics_assessment_questionnaire_page_7_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>conference</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Conference</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>event_logistics_assessment_questionnaire_page_2_choices</t>
+          <t>event_logistics_assessment_questionnaire_page_7_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>workshop</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Workshop</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>event_logistics_assessment_questionnaire_page_3_choices</t>
+          <t>event_logistics_assessment_questionnaire_page_7_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>festival</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Festival</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>event_logistics_assessment_questionnaire_page_3_choices</t>
+          <t>event_logistics_assessment_questionnaire_page_7_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>meeting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>event_logistics_assessment_questionnaire_page_7_choices</t>
+          <t>event_logistics_assessment_questionnaire_page_8_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>planned</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Planned</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>event_logistics_assessment_questionnaire_page_7_choices</t>
+          <t>event_logistics_assessment_questionnaire_page_8_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>In Progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>event_logistics_assessment_questionnaire_page_8_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
     </row>
